--- a/employee_directory.xlsx
+++ b/employee_directory.xlsx
@@ -24236,7 +24236,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>avi1997verma@gmail.com</t>
+          <t>Anirudh.verma@smartworlddevelopers.com</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">

--- a/employee_directory.xlsx
+++ b/employee_directory.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N626"/>
+  <dimension ref="A1:P626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,16 @@
           <t>Reporting Manager</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Extension Number</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Reporting Manager</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +549,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +611,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -643,6 +668,16 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -695,6 +730,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -747,6 +787,11 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -799,6 +844,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -851,6 +901,11 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -903,6 +958,16 @@
           <t>Rajat Jain(80106)</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6670</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rajat Jain(80106)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -955,6 +1020,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1007,6 +1077,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6639</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1059,6 +1139,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1111,6 +1196,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1163,6 +1253,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1215,6 +1310,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1267,6 +1367,16 @@
           <t>Nitin Gupta(80824)</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6616</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nitin Gupta(80824)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1319,6 +1429,11 @@
           <t>Mohit Lakhtakia(80084)</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mohit Lakhtakia(80084)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1371,6 +1486,16 @@
           <t>Anil Mittal(80456)</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6675</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Anil Mittal(80456)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1423,6 +1548,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6930</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1475,6 +1610,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1527,6 +1667,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1579,6 +1724,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1631,6 +1786,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1683,6 +1843,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1735,6 +1900,16 @@
           <t>Anil Mittal(80456)</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Anil Mittal(80456)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1787,6 +1962,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1839,6 +2024,16 @@
           <t>Rajat Jain(80106)</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6605</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rajat Jain(80106)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1891,6 +2086,16 @@
           <t>Rajat Jain(80106)</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rajat Jain(80106)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1943,6 +2148,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1995,6 +2205,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2047,6 +2262,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2099,6 +2319,16 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2151,6 +2381,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2203,6 +2443,11 @@
           <t>Akhilender Kumar Gupta(80362)</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Akhilender Kumar Gupta(80362)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2255,6 +2500,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2307,6 +2562,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2359,6 +2619,16 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2411,6 +2681,16 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6617</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2463,6 +2743,16 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2515,6 +2805,11 @@
           <t>Yash Sharma(80061)</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Yash Sharma(80061)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2567,6 +2862,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2619,6 +2919,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2671,6 +2976,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2723,6 +3033,16 @@
           <t>Sayantan Mondal(81177)</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sayantan Mondal(81177)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2775,6 +3095,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2827,6 +3152,16 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2879,6 +3214,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2931,6 +3276,16 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>6638</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2983,6 +3338,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3035,6 +3400,16 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3087,6 +3462,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3139,6 +3519,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3191,6 +3576,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3243,6 +3633,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3295,6 +3690,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3347,6 +3752,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3399,6 +3809,11 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3451,6 +3866,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3503,6 +3923,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3555,6 +3980,11 @@
           <t>Amit Kumar Sharma(80363)</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Amit Kumar Sharma(80363)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3607,6 +4037,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3659,6 +4094,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3711,6 +4151,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3763,6 +4208,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>6927</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3815,6 +4270,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>6711</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3867,6 +4332,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3919,6 +4394,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3971,6 +4451,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4023,6 +4513,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4075,6 +4575,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4127,6 +4637,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4179,6 +4694,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4231,6 +4756,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4283,6 +4818,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4335,6 +4880,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4387,6 +4942,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4439,6 +4999,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4491,6 +5056,11 @@
           <t>Gaurav Bansal(80160)</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gaurav Bansal(80160)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4543,6 +5113,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4595,6 +5170,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4647,6 +5227,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4699,6 +5284,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4751,6 +5346,16 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4803,6 +5408,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4855,6 +5465,16 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>6603</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4907,6 +5527,11 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4959,6 +5584,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5011,6 +5641,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5063,6 +5698,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5115,6 +5755,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5167,6 +5812,11 @@
           <t>Yash Sharma(80061)</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Yash Sharma(80061)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5219,6 +5869,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5271,6 +5926,11 @@
           <t>Deepanshu Taneja(80358)</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Deepanshu Taneja(80358)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5323,6 +5983,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5375,6 +6040,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5427,6 +6097,11 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5479,6 +6154,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5531,6 +6211,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5583,6 +6268,11 @@
           <t>Anil Gupta(80704)</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Anil Gupta(80704)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5635,6 +6325,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5687,6 +6382,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5739,6 +6439,11 @@
           <t>Neeraj Kalra(80617)</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Neeraj Kalra(80617)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5791,6 +6496,11 @@
           <t>Mohammad Waseem(80411)</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Mohammad Waseem(80411)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5843,6 +6553,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5895,6 +6610,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5947,6 +6667,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5999,6 +6724,11 @@
           <t>Sachin Suri(80357)</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Sachin Suri(80357)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6051,6 +6781,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6103,6 +6838,16 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6155,6 +6900,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6207,6 +6957,16 @@
           <t>Rajat Jain(80106)</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Rajat Jain(80106)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6259,6 +7019,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6311,6 +7076,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6363,6 +7133,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6415,6 +7190,16 @@
           <t>Mohit Lakhtakia(80084)</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Mohit Lakhtakia(80084)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6467,6 +7252,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6519,6 +7309,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6571,6 +7366,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6623,6 +7423,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6675,6 +7485,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6727,6 +7542,16 @@
           <t>Imran Khan(80405)</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>6732</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Imran Khan(80405)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6779,6 +7604,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6831,6 +7666,11 @@
           <t>Ravi Sharma(80083)</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Ravi Sharma(80083)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6883,6 +7723,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6935,6 +7785,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>6732</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6987,6 +7847,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7039,6 +7904,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7091,6 +7961,16 @@
           <t>Deepika Sapra(80008)</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Deepika Sapra(80008)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7143,6 +8023,11 @@
           <t>Deepanshu Taneja(80358)</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Deepanshu Taneja(80358)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7195,6 +8080,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7247,6 +8142,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7299,6 +8199,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7351,6 +8256,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7403,6 +8318,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7455,6 +8375,11 @@
           <t>Himanshu Dingliwal(80483)</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Himanshu Dingliwal(80483)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7507,6 +8432,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7559,6 +8489,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7611,6 +8546,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7663,6 +8603,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7715,6 +8665,11 @@
           <t>Anand Kumar Mehta(81200)</t>
         </is>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Anand Kumar Mehta(81200)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7767,6 +8722,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7819,6 +8784,16 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7871,6 +8846,16 @@
           <t>Sachin Suri(80357)</t>
         </is>
       </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>6670</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Sachin Suri(80357)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7923,6 +8908,16 @@
           <t>Paras Arora(80918)</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Paras Arora(80918)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7975,6 +8970,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8027,6 +9027,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8079,6 +9089,11 @@
           <t>Gaurav Bansal(80160)</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Gaurav Bansal(80160)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8131,6 +9146,11 @@
           <t>Anil Gupta(80704)</t>
         </is>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Anil Gupta(80704)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8183,6 +9203,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8235,6 +9260,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8287,6 +9317,11 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8339,6 +9374,16 @@
           <t>Amandeep Singh Ahuja(80331)</t>
         </is>
       </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Amandeep Singh Ahuja(80331)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8391,6 +9436,11 @@
           <t>Amandeep Singh Ahuja(80331)</t>
         </is>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Amandeep Singh Ahuja(80331)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8443,6 +9493,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8495,6 +9550,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8547,6 +9612,16 @@
           <t>Suman Lata(81125)</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Suman Lata(81125)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8599,6 +9674,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8651,6 +9731,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8703,6 +9788,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8755,6 +9845,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8807,6 +9902,11 @@
           <t>Imran Khan(80405)</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Imran Khan(80405)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8859,6 +9959,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8911,6 +10016,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8963,6 +10073,16 @@
           <t>Nitin Gupta(80824)</t>
         </is>
       </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Nitin Gupta(80824)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9015,6 +10135,11 @@
           <t>Pooja Pandita(80120)</t>
         </is>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Pooja Pandita(80120)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9067,6 +10192,11 @@
           <t>Amit Kumar Sharma(80363)</t>
         </is>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Amit Kumar Sharma(80363)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9119,6 +10249,11 @@
           <t>Ankur Gupta(81172)</t>
         </is>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Ankur Gupta(81172)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9171,6 +10306,11 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9223,6 +10363,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9275,6 +10420,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9327,6 +10477,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9379,6 +10534,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9431,6 +10596,16 @@
           <t>Nitesh Goyal(80370)</t>
         </is>
       </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Nitesh Goyal(80370)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9483,6 +10658,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9535,6 +10715,11 @@
           <t>Himanshu Dingliwal(80483)</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Himanshu Dingliwal(80483)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9587,6 +10772,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9639,6 +10829,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9691,6 +10886,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9743,6 +10948,11 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9795,6 +11005,16 @@
           <t>Neeraj Kalra(80617)</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>6632</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Neeraj Kalra(80617)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9847,6 +11067,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9899,6 +11129,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9951,6 +11186,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10003,6 +11243,11 @@
           <t>Yash Sharma(80061)</t>
         </is>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Yash Sharma(80061)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10055,6 +11300,16 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10107,6 +11362,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10159,6 +11424,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10211,6 +11481,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10263,6 +11538,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10315,6 +11595,16 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10367,6 +11657,16 @@
           <t>Khushboo Sondhi(81126)</t>
         </is>
       </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Khushboo Sondhi(81126)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10419,6 +11719,11 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10471,6 +11776,16 @@
           <t>Sachin Suri(80357)</t>
         </is>
       </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>6632</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Sachin Suri(80357)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10523,6 +11838,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10573,6 +11893,14 @@
       <c r="N195" t="e">
         <v>#N/A</v>
       </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="P195" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10625,6 +11953,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10677,6 +12010,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10729,6 +12067,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10781,6 +12124,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10833,6 +12181,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10885,6 +12238,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10937,6 +12295,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10989,6 +12352,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11041,6 +12409,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11093,6 +12471,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11145,6 +12533,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11197,6 +12590,16 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11249,6 +12652,16 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11301,6 +12714,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11353,6 +12771,11 @@
           <t>Pankaj Krishna Rane(80536)</t>
         </is>
       </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Pankaj Krishna Rane(80536)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11405,6 +12828,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11457,6 +12885,11 @@
           <t>Mohit Lakhtakia(80084)</t>
         </is>
       </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Mohit Lakhtakia(80084)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11509,6 +12942,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11561,6 +12999,16 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11613,6 +13061,11 @@
           <t>Yash Sharma(80061)</t>
         </is>
       </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Yash Sharma(80061)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11665,6 +13118,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11717,6 +13180,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11769,6 +13237,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11821,6 +13294,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11873,6 +13351,16 @@
           <t>Nitin Gupta(80824)</t>
         </is>
       </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Nitin Gupta(80824)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11925,6 +13413,16 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11977,6 +13475,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12029,6 +13532,16 @@
           <t>Garima Maheshwari(80811)</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>6915</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Garima Maheshwari(80811)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12081,6 +13594,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12133,6 +13651,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12185,6 +13708,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12237,6 +13765,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12289,6 +13822,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12341,6 +13879,16 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12393,6 +13941,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12445,6 +13998,11 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12497,6 +14055,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12549,6 +14112,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12601,6 +14169,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12653,6 +14231,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12705,6 +14288,16 @@
           <t>Anil Gupta(80704)</t>
         </is>
       </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Anil Gupta(80704)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12757,6 +14350,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12809,6 +14407,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12861,6 +14464,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12913,6 +14521,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12965,6 +14578,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13017,6 +14635,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13069,6 +14697,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13121,6 +14754,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13173,6 +14811,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13225,6 +14868,11 @@
           <t>Ravi Sharma(80083)</t>
         </is>
       </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Ravi Sharma(80083)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13277,6 +14925,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13329,6 +14982,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13381,6 +15039,11 @@
           <t>Ranjit Sarkar(80100)</t>
         </is>
       </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Ranjit Sarkar(80100)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13433,6 +15096,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13485,6 +15158,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13537,6 +15215,11 @@
           <t>Sumeet Kapoor(80601)</t>
         </is>
       </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Sumeet Kapoor(80601)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13589,6 +15272,16 @@
           <t>Avneesh Kumar Gupta(80213)</t>
         </is>
       </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Avneesh Kumar Gupta(80213)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13641,6 +15334,11 @@
           <t>Himanshu Dingliwal(80483)</t>
         </is>
       </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Himanshu Dingliwal(80483)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13693,6 +15391,11 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13745,6 +15448,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13797,6 +15510,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13849,6 +15567,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13901,6 +15624,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13953,6 +15681,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14005,6 +15738,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14057,6 +15795,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14109,6 +15852,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14161,6 +15909,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14213,6 +15966,16 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14265,6 +16028,16 @@
           <t>Sudhir Pathak(80039)</t>
         </is>
       </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Sudhir Pathak(80039)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14317,6 +16090,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14369,6 +16147,16 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14421,6 +16209,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14473,6 +16266,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14525,6 +16323,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14577,6 +16380,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14629,6 +16437,16 @@
           <t>Sharad Kumar Meena(80539)</t>
         </is>
       </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Sharad Kumar Meena(80539)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14681,6 +16499,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14733,6 +16556,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14785,6 +16613,11 @@
           <t>Amarjeet Khadulia(80981)</t>
         </is>
       </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Amarjeet Khadulia(80981)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14837,6 +16670,16 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14889,6 +16732,16 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14941,6 +16794,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14993,6 +16851,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15045,6 +16908,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15097,6 +16965,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15149,6 +17022,11 @@
           <t>Pooja Pandita(80120)</t>
         </is>
       </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Pooja Pandita(80120)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15201,6 +17079,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15253,6 +17136,11 @@
           <t>Arpit Bansal(80124)</t>
         </is>
       </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Arpit Bansal(80124)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15305,6 +17193,11 @@
           <t>Yash Sharma(80061)</t>
         </is>
       </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Yash Sharma(80061)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15357,6 +17250,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15409,6 +17312,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15461,6 +17369,11 @@
           <t>Neeha Bajpai(80018)</t>
         </is>
       </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Neeha Bajpai(80018)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15513,6 +17426,16 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15565,6 +17488,16 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15617,6 +17550,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15669,6 +17607,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>6732</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15721,6 +17669,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15773,6 +17726,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15825,6 +17783,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15877,6 +17840,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15929,6 +17897,11 @@
           <t>Anand Kumar Mehta(81200)</t>
         </is>
       </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Anand Kumar Mehta(81200)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15981,6 +17954,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16033,6 +18011,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16085,6 +18068,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16137,6 +18125,16 @@
           <t>Manish Kumar Singla(81001)</t>
         </is>
       </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Manish Kumar Singla(81001)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16189,6 +18187,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16241,6 +18244,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16293,6 +18301,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16345,6 +18358,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16397,6 +18415,11 @@
           <t>Neeha Bajpai(80018)</t>
         </is>
       </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Neeha Bajpai(80018)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16449,6 +18472,11 @@
           <t>Gaurav Bansal(80160)</t>
         </is>
       </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Gaurav Bansal(80160)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16501,6 +18529,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16553,6 +18586,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16605,6 +18643,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16657,6 +18705,16 @@
           <t>Rajat Jain(80106)</t>
         </is>
       </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Rajat Jain(80106)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16709,6 +18767,16 @@
           <t>Ravi Sharma(80083)</t>
         </is>
       </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Ravi Sharma(80083)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16761,6 +18829,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16813,6 +18886,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -16865,6 +18943,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -16917,6 +19005,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -16969,6 +19067,16 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17021,6 +19129,11 @@
           <t>Pooja Pandita(80120)</t>
         </is>
       </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Pooja Pandita(80120)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -17073,6 +19186,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17125,6 +19243,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17177,6 +19300,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17229,6 +19357,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17281,6 +19414,16 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -17333,6 +19476,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -17385,6 +19533,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -17437,6 +19590,16 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -17489,6 +19652,11 @@
           <t>Ankur Gupta(81172)</t>
         </is>
       </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Ankur Gupta(81172)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -17541,6 +19709,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -17593,6 +19766,11 @@
           <t>Garima Maheshwari(80811)</t>
         </is>
       </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>Garima Maheshwari(80811)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -17645,6 +19823,16 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -17697,6 +19885,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -17749,6 +19947,11 @@
           <t>Udit Agarwal(80894)</t>
         </is>
       </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Udit Agarwal(80894)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -17801,6 +20004,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -17853,6 +20061,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -17905,6 +20118,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -17957,6 +20175,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -18009,6 +20232,16 @@
           <t>Deepak Aggarwal(80470)</t>
         </is>
       </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>6638</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Deepak Aggarwal(80470)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18061,6 +20294,16 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18113,6 +20356,11 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18165,6 +20413,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18217,6 +20470,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>6622</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18269,6 +20532,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18321,6 +20594,16 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18373,6 +20656,11 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -18425,6 +20713,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -18477,6 +20770,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -18529,6 +20827,16 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -18581,6 +20889,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -18633,6 +20946,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -18685,6 +21003,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -18737,6 +21060,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -18789,6 +21117,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -18841,6 +21174,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -18893,6 +21231,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -18945,6 +21288,11 @@
           <t>Sayantan Mondal(81177)</t>
         </is>
       </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Sayantan Mondal(81177)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -18997,6 +21345,11 @@
           <t>Ravi Sharma(80083)</t>
         </is>
       </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Ravi Sharma(80083)</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -19049,6 +21402,16 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>6675</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19101,6 +21464,11 @@
           <t>Chandan Khurana(81150)</t>
         </is>
       </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Chandan Khurana(81150)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19153,6 +21521,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19205,6 +21578,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -19257,6 +21635,16 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>6610</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -19309,6 +21697,11 @@
           <t>Neeha Bajpai(80018)</t>
         </is>
       </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Neeha Bajpai(80018)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -19361,6 +21754,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -19413,6 +21811,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -19465,6 +21868,11 @@
           <t>Ajay Kumar Rai(80374)</t>
         </is>
       </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Ajay Kumar Rai(80374)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19517,6 +21925,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19569,6 +21982,11 @@
           <t>Amandeep Singh Ahuja(80331)</t>
         </is>
       </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>Amandeep Singh Ahuja(80331)</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -19621,6 +22039,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -19673,6 +22096,11 @@
           <t>Neeraj Kalra(80617)</t>
         </is>
       </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>Neeraj Kalra(80617)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -19725,6 +22153,11 @@
           <t>Abhishek Kumar Patel(80699)</t>
         </is>
       </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>Abhishek Kumar Patel(80699)</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -19777,6 +22210,11 @@
           <t>Paras Arora(80918)</t>
         </is>
       </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Paras Arora(80918)</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -19829,6 +22267,11 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -19881,6 +22324,16 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -19933,6 +22386,16 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -19985,6 +22448,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>6917</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20037,6 +22510,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -20089,6 +22567,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20141,6 +22624,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20193,6 +22681,16 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -20245,6 +22743,16 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -20297,6 +22805,16 @@
           <t>Deepika Sapra(80008)</t>
         </is>
       </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>6836</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Deepika Sapra(80008)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -20349,6 +22867,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -20401,6 +22924,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20453,6 +22981,16 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>6639</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -20505,6 +23043,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -20557,6 +23100,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -20609,6 +23157,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -20661,6 +23214,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20713,6 +23271,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -20765,6 +23328,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -20817,6 +23385,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -20869,6 +23442,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -20921,6 +23499,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -20973,6 +23556,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -21025,6 +23613,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21077,6 +23675,11 @@
           <t>Rajeev Kumar Agrawal(80941)</t>
         </is>
       </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar Agrawal(80941)</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -21129,6 +23732,16 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21181,6 +23794,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -21233,6 +23851,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -21285,6 +23908,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -21337,6 +23965,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21389,6 +24022,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -21441,6 +24079,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -21493,6 +24136,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -21545,6 +24193,16 @@
           <t>Saket Kumar(80380)</t>
         </is>
       </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Saket Kumar(80380)</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -21597,6 +24255,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -21649,6 +24312,11 @@
           <t>Anil Gupta(80704)</t>
         </is>
       </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Anil Gupta(80704)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -21701,6 +24369,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -21753,6 +24426,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -21805,6 +24483,16 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -21857,6 +24545,16 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -21909,6 +24607,16 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -21961,6 +24669,11 @@
           <t>Garima Maheshwari(80811)</t>
         </is>
       </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Garima Maheshwari(80811)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22013,6 +24726,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -22065,6 +24783,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22117,6 +24840,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -22169,6 +24897,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -22221,6 +24954,16 @@
           <t>Neeraj Kalra(80617)</t>
         </is>
       </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Neeraj Kalra(80617)</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -22273,6 +25016,16 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -22325,6 +25078,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -22377,6 +25135,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -22429,6 +25192,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -22481,6 +25249,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -22533,6 +25306,16 @@
           <t>Amandeep Singh Ahuja(80331)</t>
         </is>
       </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Amandeep Singh Ahuja(80331)</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -22585,6 +25368,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -22637,6 +25425,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -22689,6 +25482,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -22741,6 +25539,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -22793,6 +25596,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -22845,6 +25653,16 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22897,6 +25715,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22949,6 +25772,16 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -23001,6 +25834,11 @@
           <t>Amarjeet Khadulia(80981)</t>
         </is>
       </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>Amarjeet Khadulia(80981)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23053,6 +25891,16 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -23105,6 +25953,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -23157,6 +26010,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -23209,6 +26067,11 @@
           <t>Neeraj Kalra(80617)</t>
         </is>
       </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Neeraj Kalra(80617)</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -23261,6 +26124,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -23313,6 +26181,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -23365,6 +26238,11 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -23417,6 +26295,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -23469,6 +26352,16 @@
           <t>Anuj Shandilya(81258)</t>
         </is>
       </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>Anuj Shandilya(81258)</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -23521,6 +26414,16 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -23573,6 +26476,11 @@
           <t>Sidharth Dhingra(80606)</t>
         </is>
       </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Sidharth Dhingra(80606)</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23625,6 +26533,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -23677,6 +26590,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -23729,6 +26647,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -23781,6 +26704,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -23833,6 +26761,11 @@
           <t>Lalit Mohan Sachdeva(81008)</t>
         </is>
       </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Lalit Mohan Sachdeva(81008)</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -23885,6 +26818,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -23937,6 +26875,11 @@
           <t>Suman Lata(81125)</t>
         </is>
       </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Suman Lata(81125)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -23989,6 +26932,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -24041,6 +26989,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -24093,6 +27051,16 @@
           <t>Sayantan Mondal(81177)</t>
         </is>
       </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>6638</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Sayantan Mondal(81177)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -24145,6 +27113,16 @@
           <t>Amarjeet Khadulia(80981)</t>
         </is>
       </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>6728</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Amarjeet Khadulia(80981)</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -24197,6 +27175,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24249,6 +27232,11 @@
           <t>Anil Lal(81027)</t>
         </is>
       </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Anil Lal(81027)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24301,6 +27289,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24353,6 +27346,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24405,6 +27403,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24457,6 +27460,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24509,6 +27517,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24561,6 +27579,16 @@
           <t>Amarjeet Khadulia(80981)</t>
         </is>
       </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Amarjeet Khadulia(80981)</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24613,6 +27641,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24665,6 +27698,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24717,6 +27755,16 @@
           <t>Chandan Khurana(81150)</t>
         </is>
       </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>6857</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Chandan Khurana(81150)</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24769,6 +27817,16 @@
           <t>Anuj Kumar Goel(80051)</t>
         </is>
       </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Anuj Kumar Goel(80051)</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24821,6 +27879,16 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24873,6 +27941,16 @@
           <t>Deepika Sapra(80008)</t>
         </is>
       </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Deepika Sapra(80008)</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24925,6 +28003,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24977,6 +28060,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -25029,6 +28117,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -25081,6 +28179,16 @@
           <t>Tripti Mehrotra(80366)</t>
         </is>
       </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Tripti Mehrotra(80366)</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -25133,6 +28241,16 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>6720</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -25185,6 +28303,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -25237,6 +28360,11 @@
           <t>Anil Gupta(80704)</t>
         </is>
       </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Anil Gupta(80704)</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25289,6 +28417,16 @@
           <t>Prateek Chauhan(80161)</t>
         </is>
       </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>Prateek Chauhan(80161)</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25341,6 +28479,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -25393,6 +28536,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>6919</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25445,6 +28598,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25497,6 +28655,11 @@
           <t>Manish Kumar Singla(81001)</t>
         </is>
       </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Manish Kumar Singla(81001)</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25549,6 +28712,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25601,6 +28769,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25653,6 +28826,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25705,6 +28888,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25757,6 +28945,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25809,6 +29002,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25861,6 +29064,16 @@
           <t>Anuj Shandilya(81258)</t>
         </is>
       </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>6730</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>Anuj Shandilya(81258)</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25913,6 +29126,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -25965,6 +29183,16 @@
           <t>Avneesh Kumar Gupta(80213)</t>
         </is>
       </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Avneesh Kumar Gupta(80213)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -26017,6 +29245,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -26069,6 +29302,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -26121,6 +29364,16 @@
           <t>Anil Mittal(80456)</t>
         </is>
       </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Anil Mittal(80456)</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -26173,6 +29426,16 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -26225,6 +29488,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26277,6 +29545,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -26329,6 +29602,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -26381,6 +29659,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26433,6 +29716,11 @@
           <t>Jitender Kumar(81010)</t>
         </is>
       </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Jitender Kumar(81010)</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -26485,6 +29773,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -26537,6 +29830,16 @@
           <t>Lalit Mohan Sachdeva(81008)</t>
         </is>
       </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>6605</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>Lalit Mohan Sachdeva(81008)</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -26589,6 +29892,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -26641,6 +29949,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -26693,6 +30006,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -26745,6 +30063,11 @@
           <t>Avneesh Kumar Gupta(80213)</t>
         </is>
       </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Avneesh Kumar Gupta(80213)</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -26797,6 +30120,11 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -26849,6 +30177,11 @@
           <t>Deepak Chadha(81162)</t>
         </is>
       </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Deepak Chadha(81162)</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -26901,6 +30234,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -26953,6 +30296,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -27005,6 +30353,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -27057,6 +30410,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -27109,6 +30472,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -27161,6 +30529,16 @@
           <t>Ranjit Sarkar(80100)</t>
         </is>
       </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>Ranjit Sarkar(80100)</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -27213,6 +30591,16 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -27265,6 +30653,11 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -27317,6 +30710,11 @@
           <t>Sumeet Kapoor(80601)</t>
         </is>
       </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Sumeet Kapoor(80601)</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -27369,6 +30767,11 @@
           <t>Rohit Sehgal(81164)</t>
         </is>
       </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Rohit Sehgal(81164)</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -27421,6 +30824,11 @@
           <t>Sanjeev Kumar Sharma(81175)</t>
         </is>
       </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Sharma(81175)</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -27473,6 +30881,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -27525,6 +30938,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -27577,6 +31000,11 @@
           <t>Sujeet Ranjan Tiwari(80467)</t>
         </is>
       </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>Sujeet Ranjan Tiwari(80467)</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -27629,6 +31057,11 @@
           <t>Jyotsna Chauhan(80024)</t>
         </is>
       </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Jyotsna Chauhan(80024)</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -27681,6 +31114,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -27733,6 +31176,16 @@
           <t>Ashish Jerath(80006)</t>
         </is>
       </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>6735</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>Ashish Jerath(80006)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -27785,6 +31238,11 @@
           <t>Sajid Rafique(80876)</t>
         </is>
       </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>Sajid Rafique(80876)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -27837,6 +31295,16 @@
           <t>Deepak Chadha(81162)</t>
         </is>
       </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>Deepak Chadha(81162)</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -27889,6 +31357,11 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -27941,6 +31414,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -27993,6 +31471,11 @@
           <t>Rohit Mehta(80770)</t>
         </is>
       </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>Rohit Mehta(80770)</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -28045,6 +31528,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -28097,6 +31585,11 @@
           <t>Paroj Dutta(81142)</t>
         </is>
       </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>Paroj Dutta(81142)</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -28149,6 +31642,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -28201,6 +31699,11 @@
           <t>Akhilender Kumar Gupta(80362)</t>
         </is>
       </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Akhilender Kumar Gupta(80362)</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -28253,6 +31756,16 @@
           <t>Sharad Kumar Meena(80539)</t>
         </is>
       </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>Sharad Kumar Meena(80539)</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -28305,6 +31818,16 @@
           <t>Nirmalya Lodh(80854)</t>
         </is>
       </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Nirmalya Lodh(80854)</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -28357,6 +31880,11 @@
           <t>Vinay Chaturvedi(80376)</t>
         </is>
       </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>Vinay Chaturvedi(80376)</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -28409,6 +31937,16 @@
           <t>Saurabh Thakur(81161)</t>
         </is>
       </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Saurabh Thakur(81161)</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -28461,6 +31999,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -28513,6 +32056,11 @@
           <t>Amit Chadha(81176)</t>
         </is>
       </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Amit Chadha(81176)</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -28565,6 +32113,11 @@
           <t>Manish Kumar Dixit(80604)</t>
         </is>
       </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>Manish Kumar Dixit(80604)</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -28617,6 +32170,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -28669,6 +32227,11 @@
           <t>Sandeep Bansal(80697)</t>
         </is>
       </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>Sandeep Bansal(80697)</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -28721,6 +32284,11 @@
           <t>Amit Chadha(81176)</t>
         </is>
       </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>Amit Chadha(81176)</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -28773,6 +32341,11 @@
           <t>Sharad Kumar Meena(80539)</t>
         </is>
       </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>Sharad Kumar Meena(80539)</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -28825,6 +32398,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -28877,6 +32460,11 @@
           <t>Sharad Kumar Meena(80539)</t>
         </is>
       </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>Sharad Kumar Meena(80539)</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -28929,6 +32517,11 @@
           <t>Pooja Pandita(80120)</t>
         </is>
       </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>Pooja Pandita(80120)</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -28981,6 +32574,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -29033,6 +32631,16 @@
           <t>Amandeep Singh Ahuja(80331)</t>
         </is>
       </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>Amandeep Singh Ahuja(80331)</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -29085,6 +32693,11 @@
           <t>Ajay Kumar(81016)</t>
         </is>
       </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>Ajay Kumar(81016)</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -29137,6 +32750,16 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -29189,6 +32812,11 @@
           <t>Ananta Narayan Nayak(80837)</t>
         </is>
       </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>Ananta Narayan Nayak(80837)</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -29241,6 +32869,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -29293,6 +32926,11 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -29345,6 +32983,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -29397,6 +33040,16 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>6828</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -29449,6 +33102,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -29501,6 +33159,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -29553,6 +33216,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -29605,6 +33273,11 @@
           <t>Paroj Dutta(81142)</t>
         </is>
       </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>Paroj Dutta(81142)</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -29657,6 +33330,11 @@
           <t>Karan Arora(81160)</t>
         </is>
       </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>Karan Arora(81160)</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -29709,6 +33387,16 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -29761,6 +33449,16 @@
           <t>Paramvir Singh Rai(80212)</t>
         </is>
       </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>Paramvir Singh Rai(80212)</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -29813,6 +33511,16 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -29865,6 +33573,11 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -29917,6 +33630,16 @@
           <t>Abhishek Singh(80871)</t>
         </is>
       </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>6638</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>Abhishek Singh(80871)</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -29969,6 +33692,11 @@
           <t>Deepak Aggarwal(80470)</t>
         </is>
       </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>Deepak Aggarwal(80470)</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -30021,6 +33749,11 @@
           <t>Arvind Aggarwal(80958)</t>
         </is>
       </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>Arvind Aggarwal(80958)</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -30073,6 +33806,11 @@
           <t>Gaurav Gandhi(80184)</t>
         </is>
       </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>Gaurav Gandhi(80184)</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -30125,6 +33863,16 @@
           <t>Deepak Aggarwal(80470)</t>
         </is>
       </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>Deepak Aggarwal(80470)</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -30177,6 +33925,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -30229,6 +33982,11 @@
           <t>Aashish Aggarwal(80847)</t>
         </is>
       </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Aashish Aggarwal(80847)</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -30281,6 +34039,16 @@
           <t>Rahul Vohra(81147)</t>
         </is>
       </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>6720</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Rahul Vohra(81147)</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -30333,6 +34101,11 @@
           <t>Nitesh Goyal(80370)</t>
         </is>
       </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Nitesh Goyal(80370)</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -30385,6 +34158,16 @@
           <t>Sudhir Pathak(80039)</t>
         </is>
       </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>6715</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Sudhir Pathak(80039)</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -30437,6 +34220,11 @@
           <t>Chamanpreet Kaur Gill(81124)</t>
         </is>
       </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Chamanpreet Kaur Gill(81124)</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -30489,6 +34277,11 @@
           <t>Deepak Aggarwal(80470)</t>
         </is>
       </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Deepak Aggarwal(80470)</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -30541,6 +34334,16 @@
           <t>Nitin Gupta(80824)</t>
         </is>
       </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Nitin Gupta(80824)</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -30593,6 +34396,16 @@
           <t>Raghav Aggarwal(90031)</t>
         </is>
       </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>6637</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Raghav Aggarwal(90031)</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -30645,6 +34458,11 @@
           <t>Saurabh Thakur(81161)</t>
         </is>
       </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Saurabh Thakur(81161)</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -30697,6 +34515,11 @@
           <t>Amarjeet Khadulia(80981)</t>
         </is>
       </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Amarjeet Khadulia(80981)</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -30749,6 +34572,11 @@
           <t>Hari Easwaran(80059)</t>
         </is>
       </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Hari Easwaran(80059)</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -30801,6 +34629,11 @@
           <t>Sayantan Mondal(81177)</t>
         </is>
       </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Sayantan Mondal(81177)</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -30853,6 +34686,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -30905,6 +34743,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -30957,6 +34800,11 @@
           <t>Sumeet Kapoor(80601)</t>
         </is>
       </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Sumeet Kapoor(80601)</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -31009,6 +34857,11 @@
           <t>Onkar Nath(80809)</t>
         </is>
       </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Onkar Nath(80809)</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -31061,6 +34914,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -31113,6 +34971,11 @@
           <t>Ranjit Sarkar(80100)</t>
         </is>
       </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Ranjit Sarkar(80100)</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -31165,6 +35028,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -31217,6 +35085,16 @@
           <t>Karan Arora(81160)</t>
         </is>
       </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>Karan Arora(81160)</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -31269,6 +35147,11 @@
           <t>Amarjit Singh(80998)</t>
         </is>
       </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>Amarjit Singh(80998)</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -31321,6 +35204,11 @@
           <t>Ravi Shekhar(81130)</t>
         </is>
       </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>Ravi Shekhar(81130)</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -31373,6 +35261,11 @@
           <t>Aditya Kaul(81224)</t>
         </is>
       </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>Aditya Kaul(81224)</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -31425,6 +35318,11 @@
           <t>Pallav Saxena(80056)</t>
         </is>
       </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>Pallav Saxena(80056)</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -31477,6 +35375,16 @@
           <t>Deepika Sapra(80008)</t>
         </is>
       </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>Deepika Sapra(80008)</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -31529,6 +35437,11 @@
           <t>Prateek Chauhan(80161)</t>
         </is>
       </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>Prateek Chauhan(80161)</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -31581,6 +35494,11 @@
           <t>Udit Kaushik(80715)</t>
         </is>
       </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>Udit Kaushik(80715)</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -31633,6 +35551,11 @@
           <t>Surender Kumar Sharma(81149)</t>
         </is>
       </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>Surender Kumar Sharma(81149)</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -31685,6 +35608,16 @@
           <t>Arun Sangwan(80872)</t>
         </is>
       </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>Arun Sangwan(80872)</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -31737,6 +35670,11 @@
           <t>Deepak Kumar(81066)</t>
         </is>
       </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>Deepak Kumar(81066)</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -31789,6 +35727,16 @@
           <t>Shashi Shankar(80335)</t>
         </is>
       </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>Shashi Shankar(80335)</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -31841,6 +35789,11 @@
           <t>Sanjeev Kumar Sharma(81175)</t>
         </is>
       </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Sharma(81175)</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -31893,6 +35846,16 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -31945,6 +35908,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -31997,6 +35965,16 @@
           <t>Himanshu Dingliwal(80483)</t>
         </is>
       </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>Himanshu Dingliwal(80483)</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -32049,6 +36027,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -32101,6 +36084,11 @@
           <t>Sanjeev Kumar Sharma(81175)</t>
         </is>
       </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Sharma(81175)</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -32153,6 +36141,11 @@
           <t>Sunil Kumar Singh(81074)</t>
         </is>
       </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Singh(81074)</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -32205,6 +36198,16 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -32257,6 +36260,11 @@
           <t>Manish Chhabra(80582)</t>
         </is>
       </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Manish Chhabra(80582)</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -32309,6 +36317,11 @@
           <t>Management Office</t>
         </is>
       </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>Management Office</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -32361,6 +36374,11 @@
           <t>Vikas Malhotra(80002)</t>
         </is>
       </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -32413,6 +36431,11 @@
           <t>Vikas Mann(80209)</t>
         </is>
       </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>Vikas Mann(80209)</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -32465,6 +36488,11 @@
           <t>Sanjeev Kumar Sharma(81175)</t>
         </is>
       </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Sharma(81175)</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -32517,6 +36545,11 @@
           <t>Yashpal Yadav(80768)</t>
         </is>
       </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Yashpal Yadav(80768)</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -32569,6 +36602,11 @@
           <t>Ritu Dua(81195)</t>
         </is>
       </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>Ritu Dua(81195)</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -32621,6 +36659,11 @@
           <t>Ravindra Kumar(80662)</t>
         </is>
       </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar(80662)</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -32673,6 +36716,11 @@
           <t>Chhater Singh Rohilla(80435)</t>
         </is>
       </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>Chhater Singh Rohilla(80435)</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -32725,6 +36773,11 @@
           <t>Amit Kamalakant Sawant(81019)</t>
         </is>
       </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Amit Kamalakant Sawant(81019)</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -32777,6 +36830,11 @@
           <t>Ashwini Sharma(81120)</t>
         </is>
       </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>Ashwini Sharma(81120)</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -32829,6 +36887,11 @@
           <t>Rohit  Kumar(80796)</t>
         </is>
       </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>Rohit  Kumar(80796)</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -32881,6 +36944,11 @@
           <t>Aishwarya Singh(81228)</t>
         </is>
       </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>Aishwarya Singh(81228)</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -32929,6 +36997,11 @@
         </is>
       </c>
       <c r="N625" t="inlineStr">
+        <is>
+          <t>Vikas Malhotra(80002)</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
         <is>
           <t>Vikas Malhotra(80002)</t>
         </is>
